--- a/data/safety_checklists.xlsx
+++ b/data/safety_checklists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -32,6 +32,15 @@
   </si>
   <si>
     <t>Created_At</t>
+  </si>
+  <si>
+    <t>f4f5362ed5a749a99fffe0c39665c8b1</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-02T20:15:04.718697</t>
   </si>
 </sst>
 </file>
@@ -389,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -412,6 +421,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/safety_checklists.xlsx
+++ b/data/safety_checklists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -37,10 +37,16 @@
     <t>f4f5362ed5a749a99fffe0c39665c8b1</t>
   </si>
   <si>
+    <t>d326b868b1d0442ab652c9787c1b6557</t>
+  </si>
+  <si>
     <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-02T20:15:04.718697</t>
+  </si>
+  <si>
+    <t>2025-12-04T18:57:51.824149</t>
   </si>
 </sst>
 </file>
@@ -398,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -426,10 +432,18 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
